--- a/storage/app/public/MOHAMED KARBOUT.xlsx
+++ b/storage/app/public/MOHAMED KARBOUT.xlsx
@@ -144,9 +144,9 @@
           <t>Anglais technique</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-03</t>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -156,22 +156,22 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>En attente</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>En attente</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>En attente</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>En attente</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
